--- a/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_vol/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_vol/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,14 +462,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.1176292611478176</v>
+        <v>-0.1013835980717065</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.2844236140519993</v>
+        <v>0.1784112843231744</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.5312322077753152</v>
+        <v>-0.6712047941246282</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.7659276917810007</v>
+        <v>-0.8811293617693703</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2183144552361733</v>
+        <v>0.1853656190055859</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.6133819191365644</v>
+        <v>-0.6138648281151698</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>41.46886639434052</v>
+        <v>37.11273003437282</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.2393526133139185</v>
+        <v>-0.03059129888697032</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2327849117508408</v>
+        <v>0.2935068280714968</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.170693637670016</v>
+        <v>-0.01508962259673319</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-1.513502218906165</v>
+        <v>-0.02181103582733411</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.2721050124838118</v>
+        <v>0.1874394050037239</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.9110579850282799</v>
+        <v>-0.1698419180177039</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>43.15739423703537</v>
+        <v>27.06428850035041</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.09707081330461864</v>
+        <v>-0.1325971395967297</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.21024016168045</v>
+        <v>0.2231833540390545</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.4720091199139138</v>
+        <v>-0.6188415122491143</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.6833260848730912</v>
+        <v>-0.8374239121229946</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.235973188736741</v>
+        <v>0.2878127817203773</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.4274751253316635</v>
+        <v>-0.4783697416436606</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>52.19395315294669</v>
+        <v>64.51732566144101</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.0861972466667138</v>
+        <v>-0.1656133801858003</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2198794600419118</v>
+        <v>0.2649304508839106</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>-0.3852976132680966</v>
+        <v>-0.6358444139503804</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-0.5496586955025019</v>
+        <v>-0.8786000778752601</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1907188371311748</v>
+        <v>0.2256198102447946</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.4697735338424188</v>
+        <v>-0.7616031555902859</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>56.87868171366596</v>
+        <v>69.41406340512974</v>
       </c>
     </row>
     <row r="6">
@@ -636,29 +636,57 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.2027538573256962</v>
+        <v>0.2692628545479079</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2478482514852154</v>
+        <v>0.265268117387686</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.8369547976175522</v>
+        <v>1.009385009703835</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.170368796412908</v>
+        <v>1.431149537174459</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1618510169540864</v>
+        <v>0.1671807681401178</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.303704659378897</v>
+        <v>1.677952096944452</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>59.45221137451779</v>
+        <v>69.77571473866693</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026年截至07-31</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0.3675364676999848</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.3747856085746062</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1.66163440835056</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>2.575948872296967</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.1491119526727829</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>5.122354962274777</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>42.04786048933482</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H6"/>
+  <autoFilter ref="A1:H7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>